--- a/data/supplementary/Supplementary_Data_S1.xlsx
+++ b/data/supplementary/Supplementary_Data_S1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ai bcrabl tki\manuscript\results\final manuscript\final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9291B505-919D-4F51-AD7D-111885425E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736F4757-A569-468A-A0CB-1204E5264582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,17 @@
     <sheet name="Top10_Main" sheetId="2" r:id="rId2"/>
     <sheet name="README" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -6332,29 +6341,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="XPUniqueTable" displayName="XPUniqueTable" ref="A1:U503" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="XPUniqueTable" displayName="XPUniqueTable" ref="A1:U503" totalsRowShown="0" dataDxfId="21">
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Record Type" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="XP Rank" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Compound" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="XP GlideScore" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Consensus predicted pIC50" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="SA Score" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Max Morgan Similarity" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Max Murcko Similarity" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canonical SMILES" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InChIKey" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Molecular Formula" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="MW" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="cLogP" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="HBD" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="HBA" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="TPSA (Å²)" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Rotatable Bonds" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Lipinski Violations" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Within ≤1 Lipinski Violation" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="PAINS Flag" dataDxfId="2"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Project Filter Pass" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Record Type" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="XP Rank" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Compound" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="XP GlideScore" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Consensus predicted pIC50" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="SA Score" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Max Morgan Similarity" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Max Murcko Similarity" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canonical SMILES" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InChIKey" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Molecular Formula" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="MW" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="cLogP" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="HBD" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="HBA" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="TPSA (Å²)" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Rotatable Bonds" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Lipinski Violations" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Within ≤1 Lipinski Violation" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="PAINS Flag" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Project Filter Pass" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11590,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="O77" s="12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P77" s="13">
         <v>124.99000000000001</v>
@@ -11602,13 +11611,13 @@
         <v>2</v>
       </c>
       <c r="S77" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T77" s="9" t="s">
         <v>27</v>
       </c>
       <c r="U77" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:21" ht="28">
